--- a/src/Tests/Samples.VerifySpreadsheetDocument.verified.xlsx
+++ b/src/Tests/Samples.VerifySpreadsheetDocument.verified.xlsx
@@ -8,7 +8,7 @@
     <workbookView xWindow="10320" yWindow="4224" windowWidth="30960" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="DeterministicId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
